--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,154 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="복약일정" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="식단목록" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="작성방법" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="복약일정" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="식단목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성방법" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
-  <si>
-    <t>시간</t>
-  </si>
-  <si>
-    <t>약이름</t>
-  </si>
-  <si>
-    <t>수량</t>
-  </si>
-  <si>
-    <t>요일</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>혈압약</t>
-  </si>
-  <si>
-    <t>1정</t>
-  </si>
-  <si>
-    <t>매일</t>
-  </si>
-  <si>
-    <t>당뇨약</t>
-  </si>
-  <si>
-    <t>2정</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>영양제</t>
-  </si>
-  <si>
-    <t>음식이름</t>
-  </si>
-  <si>
-    <t>상태</t>
-  </si>
-  <si>
-    <t>메모</t>
-  </si>
-  <si>
-    <t>자몽</t>
-  </si>
-  <si>
-    <t>금지</t>
-  </si>
-  <si>
-    <t>약사님이 절대 금지라고 함</t>
-  </si>
-  <si>
-    <t>바나나</t>
-  </si>
-  <si>
-    <t>허용</t>
-  </si>
-  <si>
-    <t>하루 1개까지 괜찮음</t>
-  </si>
-  <si>
-    <t>짠 음식</t>
-  </si>
-  <si>
-    <t>주의</t>
-  </si>
-  <si>
-    <t>가능한 싱겁게</t>
-  </si>
-  <si>
-    <t>이 파일 작성 방법</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>[복약일정] 시트</t>
-  </si>
-  <si>
-    <t>- 시간: 24시간 기준으로 08:00, 20:00 처럼 적어주세요.</t>
-  </si>
-  <si>
-    <t>- 약이름: 약 이름을 적어주세요.</t>
-  </si>
-  <si>
-    <t>- 수량: 1정, 2캡슐 처럼 적어주세요. (비워둬도 됨)</t>
-  </si>
-  <si>
-    <t>- 요일: 매일 / 평일 / 주말 / 월,수,금 처럼 적어주세요. (비워두면 매일로 등록돼요)</t>
-  </si>
-  <si>
-    <t>- 같은 시간에 여러 약이 있으면 줄을 여러 개로 나눠서 각각 적어주세요.</t>
-  </si>
-  <si>
-    <t>[식단목록] 시트</t>
-  </si>
-  <si>
-    <t>- 음식이름: 음식 이름을 적어주세요.</t>
-  </si>
-  <si>
-    <t>- 상태: 허용 / 주의 / 금지 중 하나로 적어주세요.</t>
-  </si>
-  <si>
-    <t>- 메모: 참고할 내용을 자유롭게 적어주세요. (비워둬도 됨)</t>
-  </si>
-  <si>
-    <t>다 작성하신 다음, 앱에서 "엑셀로 등록" 버튼으로 이 파일을 업로드해주세요.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
       <sz val="13"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -167,25 +52,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -510,223 +454,362 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col width="10" customWidth="1" style="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>약이름</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>요일</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>혈압약</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1정</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>당뇨약</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2정</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>영양제</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1정</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>08:00,13:00,19:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>항생제</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1정</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>음식이름</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>자몽</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>금지</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>약사님이 절대 금지라고 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>바나나</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>허용</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>하루 1개까지 괜찮음</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>짠 음식</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>가능한 싱겁게</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>사과, 배, 포도</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>한 번에 조금씩만</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="70" customWidth="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>36</v>
+    <row r="1" customFormat="1" s="4">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>이 파일 작성 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[복약일정] 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>- 시간: 24시간 기준으로 08:00, 20:00 처럼 적어주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>- 약이름: 약 이름을 적어주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>- 수량: 1정, 2캡슐 처럼 적어주세요. (비워둬도 됨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>- 요일: 매일 / 평일 / 주말 / 월,수,금 처럼 적어주세요. (비워두면 매일로 등록돼요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>- 같은 시간에 여러 약이 있으면 줄을 여러 개로 나눠서 각각 적어주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>- 하루에 여러 번(아침/점심/저녁) 먹는 같은 약은, 시간 칸에 08:00,13:00,19:00 처럼 콤마(,)로 이어 적으면 한 번에 등록돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>[식단목록] 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>- 음식이름: 음식 이름을 적어주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>- 상태: 허용 / 주의 / 금지 중 하나로 적어주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>- 메모: 참고할 내용을 자유롭게 적어주세요. (비워둬도 됨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>- 같은 상태/메모로 여러 음식을 한 번에 등록하려면, 음식이름 칸에 사과, 배, 포도 처럼 콤마(,)로 이어 적으면 각각 따로 등록돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>다 작성하신 다음, 앱에서 "엑셀로 등록" 버튼으로 이 파일을 업로드해주세요.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>